--- a/Assignmet_5_Self_Evaluation.xlsx
+++ b/Assignmet_5_Self_Evaluation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lohbc\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\4timothy\Desktop\github\personal\NA5-WATX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEFADB76-5A4E-4EFF-97B3-B890A68803B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFDC9CC1-6811-4F1F-8B47-8A1CDC426920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29250" yWindow="4560" windowWidth="28800" windowHeight="15345" xr2:uid="{7F861FE8-DB62-4E15-8E3F-F7664C3DFDF7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F861FE8-DB62-4E15-8E3F-F7664C3DFDF7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -42,9 +45,6 @@
   </si>
   <si>
     <t>Group:</t>
-  </si>
-  <si>
-    <t>Loh Boon Cheong, Timothy | Alfred Lo Kai Xuan | William Wibisana Dumanauw | Xavier Koh Zhi Kuang</t>
   </si>
   <si>
     <t>Reviewer Name</t>
@@ -139,6 +139,9 @@
   <si>
     <t>Comment on each member's working attitude, learning ability, team work.
 No need to comment yourself here.</t>
+  </si>
+  <si>
+    <t>4 Guys 1 Stroke</t>
   </si>
 </sst>
 </file>
@@ -308,11 +311,53 @@
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -322,48 +367,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -703,7 +706,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8B867CC-2C44-4B91-8B1F-67E51723A738}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" customWidth="1"/>
@@ -718,51 +721,51 @@
   <sheetData>
     <row r="1" spans="4:9" x14ac:dyDescent="0.25"/>
     <row r="2" spans="4:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
     </row>
     <row r="3" spans="4:9" x14ac:dyDescent="0.25"/>
     <row r="4" spans="4:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="E4" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
     </row>
     <row r="5" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D5" s="20"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
     </row>
     <row r="6" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D6" s="20"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
     </row>
     <row r="7" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D7" s="20"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
     </row>
     <row r="8" spans="4:9" x14ac:dyDescent="0.25">
       <c r="E8" s="21"/>
@@ -780,7 +783,7 @@
     </row>
     <row r="10" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D10" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" s="21"/>
       <c r="F10" s="21"/>
@@ -796,152 +799,152 @@
       <c r="I11" s="21"/>
     </row>
     <row r="12" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+    </row>
+    <row r="13" spans="4:9" ht="58.5" x14ac:dyDescent="0.25">
+      <c r="D13" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-    </row>
-    <row r="13" spans="4:9" ht="58.5" x14ac:dyDescent="0.25">
-      <c r="D13" s="7" t="s">
+      <c r="E13" s="10"/>
+      <c r="F13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="8" t="s">
+      <c r="G13" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="H13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H13" s="9" t="s">
+    </row>
+    <row r="14" spans="4:9" ht="48" x14ac:dyDescent="0.25">
+      <c r="D14" s="11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="14" spans="4:9" ht="48" x14ac:dyDescent="0.25">
-      <c r="D14" s="10" t="s">
+      <c r="E14" s="12"/>
+      <c r="F14" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="11"/>
-      <c r="F14" s="12">
+      <c r="H14" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="4:9" ht="36" x14ac:dyDescent="0.25">
+      <c r="D15" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="12"/>
+      <c r="F15" s="4">
         <v>0.25</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="4:9" ht="36" x14ac:dyDescent="0.25">
-      <c r="D15" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="11"/>
-      <c r="F15" s="12">
+    </row>
+    <row r="16" spans="4:9" ht="72" x14ac:dyDescent="0.25">
+      <c r="D16" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="12"/>
+      <c r="F16" s="4">
         <v>0.25</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H15" s="14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="4:9" ht="72" x14ac:dyDescent="0.25">
-      <c r="D16" s="11" t="s">
+      <c r="G16" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="11"/>
-      <c r="F16" s="12">
+      <c r="H16" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="4:8" ht="72" x14ac:dyDescent="0.25">
+      <c r="D17" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="12"/>
+      <c r="F17" s="4">
         <v>0.25</v>
       </c>
-      <c r="G16" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="4:8" ht="72" x14ac:dyDescent="0.25">
-      <c r="D17" s="11" t="s">
+      <c r="G17" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E17" s="11"/>
-      <c r="F17" s="12">
-        <v>0.25</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="H17" s="14" t="s">
-        <v>11</v>
+      <c r="H17" s="6" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="4:8" x14ac:dyDescent="0.25"/>
     <row r="19" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+    </row>
+    <row r="20" spans="4:8" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D20" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-    </row>
-    <row r="20" spans="4:8" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D20" s="17" t="s">
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="18" t="s">
+      <c r="H20" s="8"/>
+    </row>
+    <row r="21" spans="4:8" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D21" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="H20" s="18"/>
-    </row>
-    <row r="21" spans="4:8" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D21" s="17" t="s">
+      <c r="H21" s="9"/>
+    </row>
+    <row r="22" spans="4:8" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D22" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="19" t="s">
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="H21" s="19"/>
-    </row>
-    <row r="22" spans="4:8" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D22" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="H22" s="19"/>
+      <c r="H22" s="9"/>
     </row>
     <row r="23" spans="4:8" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="E4:I7"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="E8:I11"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:E17"/>
     <mergeCell ref="D20:F20"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="D21:F21"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="D22:F22"/>
     <mergeCell ref="G22:H22"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="E4:I7"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="E8:I11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
